--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_3/epoch_10/per_file_predictions_epoch_10.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_3/epoch_10/per_file_predictions_epoch_10.xlsx
@@ -811,24 +811,27 @@
     <t>0,0,0,1</t>
   </si>
   <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0,0,1,0</t>
+  </si>
+  <si>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>0,1,0,0</t>
+  </si>
+  <si>
+    <t>0,0,1,1</t>
+  </si>
+  <si>
+    <t>0,1,1,0</t>
+  </si>
+  <si>
     <t>1,0,0,0</t>
   </si>
   <si>
-    <t>0,0,1,0</t>
-  </si>
-  <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0,1,0,0</t>
-  </si>
-  <si>
-    <t>0,0,1,1</t>
-  </si>
-  <si>
-    <t>0,1,1,0</t>
-  </si>
-  <si>
     <t>0.0411,0.0002,0.0010,0.9886</t>
   </si>
   <si>
@@ -880,25 +883,25 @@
     <t>0.0099,0.0001,0.0005,0.9981</t>
   </si>
   <si>
-    <t>0.0390,0.0141,0.0075,0.9701</t>
+    <t>0.0391,0.0141,0.0075,0.9700</t>
   </si>
   <si>
     <t>0.0094,0.0012,0.0009,0.9973</t>
   </si>
   <si>
-    <t>0.1568,0.0014,0.0017,0.9268</t>
-  </si>
-  <si>
-    <t>0.0126,0.0004,0.0005,0.9974</t>
-  </si>
-  <si>
-    <t>0.3509,0.2144,0.0558,0.2380</t>
+    <t>0.1570,0.0014,0.0017,0.9268</t>
+  </si>
+  <si>
+    <t>0.0127,0.0004,0.0005,0.9974</t>
+  </si>
+  <si>
+    <t>0.3510,0.2146,0.0558,0.2377</t>
   </si>
   <si>
     <t>0.0034,0.0001,0.0004,0.9995</t>
   </si>
   <si>
-    <t>0.0092,0.0007,0.0054,0.9970</t>
+    <t>0.0092,0.0007,0.0054,0.9969</t>
   </si>
   <si>
     <t>0.0063,0.0001,0.0022,0.9980</t>
@@ -916,7 +919,7 @@
     <t>0.0070,0.0006,0.0364,0.9883</t>
   </si>
   <si>
-    <t>0.0247,0.0003,0.0006,0.9942</t>
+    <t>0.0248,0.0003,0.0006,0.9942</t>
   </si>
   <si>
     <t>0.0077,0.0001,0.0004,0.9987</t>
@@ -931,55 +934,55 @@
     <t>0.0054,0.0000,0.0001,0.9992</t>
   </si>
   <si>
-    <t>0.0095,0.0001,0.0003,0.9983</t>
-  </si>
-  <si>
-    <t>0.0643,0.0026,0.0026,0.9751</t>
-  </si>
-  <si>
-    <t>0.0724,0.0007,0.0012,0.9722</t>
-  </si>
-  <si>
-    <t>0.0054,0.0125,0.2258,0.8738</t>
+    <t>0.0096,0.0001,0.0003,0.9983</t>
+  </si>
+  <si>
+    <t>0.0644,0.0026,0.0026,0.9751</t>
+  </si>
+  <si>
+    <t>0.0725,0.0007,0.0012,0.9722</t>
+  </si>
+  <si>
+    <t>0.0054,0.0125,0.2257,0.8738</t>
   </si>
   <si>
     <t>0.0175,0.0004,0.8612,0.0147</t>
   </si>
   <si>
-    <t>0.0256,0.0045,0.2180,0.8629</t>
+    <t>0.0256,0.0045,0.2180,0.8628</t>
   </si>
   <si>
     <t>0.0079,0.0000,0.0015,0.9962</t>
   </si>
   <si>
-    <t>0.0125,0.0093,0.0995,0.9661</t>
-  </si>
-  <si>
-    <t>0.0330,0.0295,0.2508,0.4446</t>
-  </si>
-  <si>
-    <t>0.0142,0.0018,0.2524,0.8496</t>
+    <t>0.0125,0.0093,0.0995,0.9660</t>
+  </si>
+  <si>
+    <t>0.0329,0.0295,0.2508,0.4445</t>
+  </si>
+  <si>
+    <t>0.0142,0.0018,0.2524,0.8495</t>
   </si>
   <si>
     <t>0.0017,0.0002,0.0003,0.9997</t>
   </si>
   <si>
-    <t>0.0040,0.5901,0.0196,0.7872</t>
-  </si>
-  <si>
-    <t>0.0169,0.7418,0.0703,0.4216</t>
-  </si>
-  <si>
-    <t>0.0217,0.7616,0.0893,0.3347</t>
-  </si>
-  <si>
-    <t>0.0020,0.0012,0.4145,0.8620</t>
+    <t>0.0040,0.5902,0.0196,0.7871</t>
+  </si>
+  <si>
+    <t>0.0169,0.7421,0.0703,0.4211</t>
+  </si>
+  <si>
+    <t>0.0217,0.7619,0.0893,0.3343</t>
+  </si>
+  <si>
+    <t>0.0020,0.0012,0.4145,0.8619</t>
   </si>
   <si>
     <t>0.0095,0.0019,0.2051,0.9303</t>
   </si>
   <si>
-    <t>0.0109,0.0014,0.0286,0.9905</t>
+    <t>0.0109,0.0014,0.0287,0.9905</t>
   </si>
   <si>
     <t>0.0071,0.0002,0.0022,0.9976</t>
@@ -994,10 +997,10 @@
     <t>0.0023,0.0001,0.0001,0.9997</t>
   </si>
   <si>
-    <t>0.0022,0.0000,0.0001,0.9998</t>
-  </si>
-  <si>
-    <t>0.0108,0.0002,0.0003,0.9981</t>
+    <t>0.0022,0.0000,0.0001,0.9997</t>
+  </si>
+  <si>
+    <t>0.0109,0.0002,0.0003,0.9981</t>
   </si>
   <si>
     <t>0.0024,0.0001,0.0003,0.9996</t>
@@ -1012,16 +1015,16 @@
     <t>0.0038,0.0000,0.0001,0.9995</t>
   </si>
   <si>
-    <t>0.0019,0.9076,0.3457,0.0234</t>
-  </si>
-  <si>
-    <t>0.0039,0.0066,0.6696,0.5065</t>
+    <t>0.0019,0.9077,0.3457,0.0234</t>
+  </si>
+  <si>
+    <t>0.0039,0.0066,0.6695,0.5064</t>
   </si>
   <si>
     <t>0.0023,0.0054,0.4413,0.8161</t>
   </si>
   <si>
-    <t>0.0149,0.1490,0.7217,0.0366</t>
+    <t>0.0149,0.1493,0.7217,0.0366</t>
   </si>
   <si>
     <t>0.0291,0.0001,0.8985,0.0006</t>
@@ -1030,28 +1033,28 @@
     <t>0.0082,0.0033,0.0045,0.9964</t>
   </si>
   <si>
-    <t>0.0021,0.7431,0.0362,0.4779</t>
-  </si>
-  <si>
-    <t>0.0674,0.0002,0.0007,0.9794</t>
-  </si>
-  <si>
-    <t>0.0996,0.0013,0.0044,0.9545</t>
-  </si>
-  <si>
-    <t>0.0083,0.0017,0.0081,0.9961</t>
-  </si>
-  <si>
-    <t>0.0066,0.2620,0.6317,0.1187</t>
-  </si>
-  <si>
-    <t>0.0147,0.3582,0.7356,0.0426</t>
-  </si>
-  <si>
-    <t>0.0030,0.9653,0.2569,0.0103</t>
-  </si>
-  <si>
-    <t>0.0058,0.0989,0.5790,0.2403</t>
+    <t>0.0021,0.7435,0.0362,0.4774</t>
+  </si>
+  <si>
+    <t>0.0675,0.0002,0.0007,0.9793</t>
+  </si>
+  <si>
+    <t>0.0997,0.0013,0.0044,0.9545</t>
+  </si>
+  <si>
+    <t>0.0083,0.0017,0.0082,0.9961</t>
+  </si>
+  <si>
+    <t>0.0066,0.2623,0.6317,0.1186</t>
+  </si>
+  <si>
+    <t>0.0147,0.3585,0.7356,0.0426</t>
+  </si>
+  <si>
+    <t>0.0030,0.9653,0.2568,0.0103</t>
+  </si>
+  <si>
+    <t>0.0058,0.0991,0.5789,0.2402</t>
   </si>
   <si>
     <t>0.0005,0.0000,0.0001,1.0000</t>
@@ -1069,28 +1072,28 @@
     <t>0.0003,0.0000,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.0153,0.4341,0.3848,0.1860</t>
-  </si>
-  <si>
-    <t>0.0053,0.1190,0.7611,0.0947</t>
-  </si>
-  <si>
-    <t>0.0087,0.0536,0.1974,0.8495</t>
-  </si>
-  <si>
-    <t>0.0114,0.0206,0.5238,0.5702</t>
-  </si>
-  <si>
-    <t>0.0032,0.6885,0.6483,0.0191</t>
-  </si>
-  <si>
-    <t>0.0182,0.1095,0.2397,0.7089</t>
+    <t>0.0153,0.4346,0.3847,0.1858</t>
+  </si>
+  <si>
+    <t>0.0053,0.1192,0.7611,0.0946</t>
+  </si>
+  <si>
+    <t>0.0087,0.0536,0.1974,0.8494</t>
+  </si>
+  <si>
+    <t>0.0114,0.0206,0.5236,0.5701</t>
+  </si>
+  <si>
+    <t>0.0032,0.6889,0.6482,0.0191</t>
+  </si>
+  <si>
+    <t>0.0182,0.1096,0.2397,0.7088</t>
   </si>
   <si>
     <t>0.0033,0.0001,0.0001,0.9996</t>
   </si>
   <si>
-    <t>0.2910,0.0002,0.0004,0.8698</t>
+    <t>0.2914,0.0002,0.0004,0.8695</t>
   </si>
   <si>
     <t>0.0011,0.0001,0.0001,0.9999</t>
@@ -1099,7 +1102,7 @@
     <t>0.0015,0.0001,0.0001,0.9998</t>
   </si>
   <si>
-    <t>0.6729,0.0002,0.0007,0.4050</t>
+    <t>0.6733,0.0002,0.0007,0.4045</t>
   </si>
   <si>
     <t>0.0018,0.0001,0.0001,0.9998</t>
@@ -1111,7 +1114,7 @@
     <t>0.0020,0.0001,0.0001,0.9998</t>
   </si>
   <si>
-    <t>0.1748,0.0001,0.0002,0.9418</t>
+    <t>0.1751,0.0001,0.0002,0.9417</t>
   </si>
   <si>
     <t>0.0009,0.0000,0.0000,0.9999</t>
@@ -1123,7 +1126,7 @@
     <t>0.0096,0.0001,0.0001,0.9986</t>
   </si>
   <si>
-    <t>0.9247,0.0002,0.0009,0.0467</t>
+    <t>0.9247,0.0002,0.0009,0.0466</t>
   </si>
   <si>
     <t>0.0059,0.0001,0.0001,0.9992</t>
@@ -1132,7 +1135,7 @@
     <t>0.0025,0.0001,0.0001,0.9997</t>
   </si>
   <si>
-    <t>0.0048,0.0003,0.0154,0.9942</t>
+    <t>0.0049,0.0003,0.0154,0.9942</t>
   </si>
   <si>
     <t>0.0081,0.0002,0.0020,0.9975</t>
@@ -1150,7 +1153,7 @@
     <t>0.0086,0.0128,0.0038,0.9937</t>
   </si>
   <si>
-    <t>0.0590,0.0021,0.0019,0.9773</t>
+    <t>0.0591,0.0021,0.0019,0.9773</t>
   </si>
   <si>
     <t>0.0174,0.0016,0.0014,0.9946</t>
@@ -1159,7 +1162,7 @@
     <t>0.0084,0.0042,0.0021,0.9963</t>
   </si>
   <si>
-    <t>0.0029,0.1041,0.0063,0.9867</t>
+    <t>0.0029,0.1042,0.0063,0.9867</t>
   </si>
   <si>
     <t>0.0106,0.0006,0.0005,0.9976</t>
@@ -1168,7 +1171,7 @@
     <t>0.0078,0.0006,0.0011,0.9982</t>
   </si>
   <si>
-    <t>0.0095,0.0008,0.0066,0.9967</t>
+    <t>0.0096,0.0008,0.0066,0.9967</t>
   </si>
   <si>
     <t>0.0130,0.0012,0.0042,0.9955</t>
@@ -1180,31 +1183,31 @@
     <t>0.0377,0.0027,0.0149,0.9772</t>
   </si>
   <si>
-    <t>0.0049,0.6417,0.0267,0.7189</t>
-  </si>
-  <si>
-    <t>0.0041,0.7320,0.0284,0.6333</t>
+    <t>0.0049,0.6419,0.0268,0.7186</t>
+  </si>
+  <si>
+    <t>0.0041,0.7323,0.0284,0.6329</t>
   </si>
   <si>
     <t>0.0080,0.0087,0.0049,0.9952</t>
   </si>
   <si>
-    <t>0.0033,0.8762,0.0749,0.1523</t>
-  </si>
-  <si>
-    <t>0.1579,0.0052,0.0058,0.9004</t>
+    <t>0.0033,0.8763,0.0749,0.1521</t>
+  </si>
+  <si>
+    <t>0.1581,0.0053,0.0058,0.9002</t>
   </si>
   <si>
     <t>0.0281,0.0004,0.0006,0.9935</t>
   </si>
   <si>
-    <t>0.0287,0.0006,0.0008,0.9929</t>
+    <t>0.0288,0.0006,0.0008,0.9929</t>
   </si>
   <si>
     <t>0.0127,0.0000,0.0001,0.9982</t>
   </si>
   <si>
-    <t>0.0426,0.0001,0.0002,0.9909</t>
+    <t>0.0426,0.0001,0.0003,0.9908</t>
   </si>
   <si>
     <t>0.0039,0.0001,0.0001,0.9995</t>
@@ -1213,7 +1216,7 @@
     <t>0.0093,0.0001,0.0002,0.9985</t>
   </si>
   <si>
-    <t>0.8048,0.0001,0.0007,0.1991</t>
+    <t>0.8050,0.0001,0.0007,0.1988</t>
   </si>
   <si>
     <t>0.0163,0.0000,0.0001,0.9972</t>
@@ -1222,16 +1225,16 @@
     <t>0.0014,0.0000,0.0001,0.9999</t>
   </si>
   <si>
-    <t>0.0074,0.0132,0.2314,0.8878</t>
-  </si>
-  <si>
-    <t>0.0162,0.1091,0.7833,0.0880</t>
+    <t>0.0074,0.0133,0.2314,0.8877</t>
+  </si>
+  <si>
+    <t>0.0162,0.1092,0.7832,0.0879</t>
   </si>
   <si>
     <t>0.0082,0.0051,0.8884,0.0437</t>
   </si>
   <si>
-    <t>0.0246,0.0039,0.1070,0.9499</t>
+    <t>0.0247,0.0039,0.1070,0.9499</t>
   </si>
   <si>
     <t>0.0062,0.0001,0.0003,0.9990</t>
@@ -1252,7 +1255,7 @@
     <t>0.0007,0.0000,0.0001,0.9999</t>
   </si>
   <si>
-    <t>0.0035,0.1275,0.3489,0.4246</t>
+    <t>0.0035,0.1277,0.3489,0.4243</t>
   </si>
   <si>
     <t>0.0021,0.0000,0.0001,0.9998</t>
@@ -1273,13 +1276,13 @@
     <t>0.6715,0.0000,0.0650,0.0000</t>
   </si>
   <si>
-    <t>0.4996,0.0000,0.0141,0.0017</t>
+    <t>0.4997,0.0000,0.0141,0.0017</t>
   </si>
   <si>
     <t>0.7585,0.0000,0.0389,0.0000</t>
   </si>
   <si>
-    <t>0.0778,0.0000,0.0005,0.9279</t>
+    <t>0.0778,0.0000,0.0005,0.9278</t>
   </si>
   <si>
     <t>0.0382,0.0001,0.0004,0.9903</t>
@@ -1291,19 +1294,19 @@
     <t>0.0057,0.0002,0.0003,0.9991</t>
   </si>
   <si>
-    <t>0.0332,0.0002,0.0005,0.9921</t>
+    <t>0.0332,0.0002,0.0005,0.9920</t>
   </si>
   <si>
     <t>0.0028,0.0006,0.0007,0.9994</t>
   </si>
   <si>
-    <t>0.0087,0.0002,0.0003,0.9985</t>
-  </si>
-  <si>
-    <t>0.1056,0.0007,0.0021,0.9582</t>
-  </si>
-  <si>
-    <t>0.0373,0.0001,0.0002,0.9925</t>
+    <t>0.0087,0.0002,0.0004,0.9985</t>
+  </si>
+  <si>
+    <t>0.1057,0.0007,0.0021,0.9581</t>
+  </si>
+  <si>
+    <t>0.0374,0.0001,0.0002,0.9925</t>
   </si>
   <si>
     <t>0.0031,0.0001,0.0001,0.9996</t>
@@ -1315,13 +1318,13 @@
     <t>0.0027,0.0001,0.0001,0.9997</t>
   </si>
   <si>
-    <t>0.0028,0.0001,0.0002,0.9997</t>
+    <t>0.0028,0.0001,0.0002,0.9996</t>
   </si>
   <si>
     <t>0.0013,0.0000,0.0000,0.9999</t>
   </si>
   <si>
-    <t>0.0531,0.0006,0.0008,0.9855</t>
+    <t>0.0532,0.0006,0.0008,0.9854</t>
   </si>
   <si>
     <t>0.0271,0.0010,0.0014,0.9929</t>
@@ -1345,10 +1348,10 @@
     <t>0.0016,0.0004,0.0290,0.9946</t>
   </si>
   <si>
-    <t>0.0028,0.0009,0.0270,0.9966</t>
-  </si>
-  <si>
-    <t>0.0055,0.0001,0.0009,0.9985</t>
+    <t>0.0028,0.0009,0.0271,0.9966</t>
+  </si>
+  <si>
+    <t>0.0056,0.0001,0.0009,0.9985</t>
   </si>
   <si>
     <t>0.0040,0.0019,0.0600,0.9906</t>
@@ -1366,28 +1369,28 @@
     <t>0.0117,0.0009,0.0050,0.9963</t>
   </si>
   <si>
-    <t>0.0130,0.0005,0.0037,0.9961</t>
+    <t>0.0130,0.0005,0.0037,0.9960</t>
   </si>
   <si>
     <t>0.0093,0.0011,0.0024,0.9971</t>
   </si>
   <si>
-    <t>0.0096,0.0013,0.0036,0.9966</t>
+    <t>0.0097,0.0013,0.0037,0.9966</t>
   </si>
   <si>
     <t>0.0085,0.0013,0.0039,0.9972</t>
   </si>
   <si>
-    <t>0.0764,0.0018,0.0190,0.9475</t>
+    <t>0.0765,0.0018,0.0190,0.9474</t>
   </si>
   <si>
     <t>0.0051,0.0007,0.0018,0.9987</t>
   </si>
   <si>
-    <t>0.0307,0.0019,0.0091,0.9858</t>
-  </si>
-  <si>
-    <t>0.2099,0.0005,0.0012,0.9014</t>
+    <t>0.0308,0.0019,0.0091,0.9857</t>
+  </si>
+  <si>
+    <t>0.2101,0.0005,0.0012,0.9012</t>
   </si>
   <si>
     <t>0.0058,0.0005,0.0005,0.9989</t>
@@ -1408,7 +1411,7 @@
     <t>0.0041,0.0004,0.0015,0.9991</t>
   </si>
   <si>
-    <t>0.0842,0.0007,0.0136,0.9301</t>
+    <t>0.0843,0.0007,0.0136,0.9300</t>
   </si>
   <si>
     <t>0.0053,0.0002,0.0007,0.9990</t>
@@ -1423,16 +1426,16 @@
     <t>0.0069,0.0002,0.0073,0.9959</t>
   </si>
   <si>
-    <t>0.0139,0.0033,0.5801,0.4830</t>
-  </si>
-  <si>
-    <t>0.0147,0.0009,0.1118,0.9326</t>
+    <t>0.0139,0.0033,0.5801,0.4829</t>
+  </si>
+  <si>
+    <t>0.0147,0.0009,0.1118,0.9325</t>
   </si>
   <si>
     <t>0.0019,0.0001,0.0001,0.9998</t>
   </si>
   <si>
-    <t>0.0586,0.0001,0.0002,0.9868</t>
+    <t>0.0587,0.0001,0.0002,0.9868</t>
   </si>
   <si>
     <t>0.0036,0.0001,0.0001,0.9995</t>
@@ -1450,7 +1453,7 @@
     <t>0.0090,0.0002,0.0006,0.9982</t>
   </si>
   <si>
-    <t>0.0117,0.0015,0.5983,0.3811</t>
+    <t>0.0117,0.0015,0.5984,0.3809</t>
   </si>
   <si>
     <t>0.0010,0.0008,0.1702,0.9717</t>
@@ -1459,16 +1462,16 @@
     <t>0.0041,0.0013,0.0115,0.9979</t>
   </si>
   <si>
-    <t>0.0023,0.0004,0.8979,0.0769</t>
+    <t>0.0023,0.0004,0.8979,0.0768</t>
   </si>
   <si>
     <t>0.0178,0.0042,0.0433,0.9865</t>
   </si>
   <si>
-    <t>0.0009,0.0003,0.9564,0.0290</t>
-  </si>
-  <si>
-    <t>0.0048,0.0021,0.1663,0.9577</t>
+    <t>0.0009,0.0003,0.9565,0.0290</t>
+  </si>
+  <si>
+    <t>0.0048,0.0021,0.1664,0.9577</t>
   </si>
   <si>
     <t>0.0089,0.0019,0.0078,0.9964</t>
@@ -1498,7 +1501,7 @@
     <t>0.0181,0.0052,0.0463,0.9849</t>
   </si>
   <si>
-    <t>0.0106,0.0049,0.1536,0.9528</t>
+    <t>0.0106,0.0049,0.1535,0.9528</t>
   </si>
   <si>
     <t>0.0114,0.0031,0.2769,0.8746</t>
@@ -1507,7 +1510,7 @@
     <t>0.0067,0.0018,0.0123,0.9967</t>
   </si>
   <si>
-    <t>0.0173,0.0002,0.0307,0.9684</t>
+    <t>0.0173,0.0002,0.0307,0.9683</t>
   </si>
   <si>
     <t>0.0015,0.0000,0.0001,0.9997</t>
@@ -1522,9 +1525,6 @@
     <t>0.0163,0.0001,0.0003,0.9968</t>
   </si>
   <si>
-    <t>0.0028,0.0001,0.0002,0.9996</t>
-  </si>
-  <si>
     <t>0.0006,0.0000,0.0001,0.9999</t>
   </si>
   <si>
@@ -1534,7 +1534,7 @@
     <t>0.0010,0.0001,0.0001,0.9999</t>
   </si>
   <si>
-    <t>0.0554,0.0005,0.0021,0.9808</t>
+    <t>0.0555,0.0005,0.0021,0.9808</t>
   </si>
 </sst>
 </file>
@@ -1920,7 +1920,7 @@
         <v>264</v>
       </c>
       <c r="D2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1934,7 +1934,7 @@
         <v>264</v>
       </c>
       <c r="D3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1948,7 +1948,7 @@
         <v>264</v>
       </c>
       <c r="D4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1962,7 +1962,7 @@
         <v>264</v>
       </c>
       <c r="D5" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1976,7 +1976,7 @@
         <v>264</v>
       </c>
       <c r="D6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1990,7 +1990,7 @@
         <v>264</v>
       </c>
       <c r="D7" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2004,7 +2004,7 @@
         <v>264</v>
       </c>
       <c r="D8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2018,7 +2018,7 @@
         <v>264</v>
       </c>
       <c r="D9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2032,7 +2032,7 @@
         <v>264</v>
       </c>
       <c r="D10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2046,7 +2046,7 @@
         <v>264</v>
       </c>
       <c r="D11" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2060,7 +2060,7 @@
         <v>264</v>
       </c>
       <c r="D12" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2074,7 +2074,7 @@
         <v>264</v>
       </c>
       <c r="D13" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2088,7 +2088,7 @@
         <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2102,7 +2102,7 @@
         <v>264</v>
       </c>
       <c r="D15" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2116,7 +2116,7 @@
         <v>264</v>
       </c>
       <c r="D16" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2130,7 +2130,7 @@
         <v>264</v>
       </c>
       <c r="D17" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2144,7 +2144,7 @@
         <v>264</v>
       </c>
       <c r="D18" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2158,7 +2158,7 @@
         <v>264</v>
       </c>
       <c r="D19" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2172,7 +2172,7 @@
         <v>264</v>
       </c>
       <c r="D20" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2186,7 +2186,7 @@
         <v>264</v>
       </c>
       <c r="D21" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2200,7 +2200,7 @@
         <v>264</v>
       </c>
       <c r="D22" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2214,7 +2214,7 @@
         <v>265</v>
       </c>
       <c r="D23" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2228,7 +2228,7 @@
         <v>264</v>
       </c>
       <c r="D24" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2242,7 +2242,7 @@
         <v>264</v>
       </c>
       <c r="D25" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2256,7 +2256,7 @@
         <v>264</v>
       </c>
       <c r="D26" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2270,7 +2270,7 @@
         <v>264</v>
       </c>
       <c r="D27" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2284,7 +2284,7 @@
         <v>264</v>
       </c>
       <c r="D28" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2298,7 +2298,7 @@
         <v>264</v>
       </c>
       <c r="D29" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2312,7 +2312,7 @@
         <v>264</v>
       </c>
       <c r="D30" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2326,7 +2326,7 @@
         <v>264</v>
       </c>
       <c r="D31" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2340,7 +2340,7 @@
         <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2354,7 +2354,7 @@
         <v>264</v>
       </c>
       <c r="D33" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2368,7 +2368,7 @@
         <v>264</v>
       </c>
       <c r="D34" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2382,7 +2382,7 @@
         <v>264</v>
       </c>
       <c r="D35" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2396,7 +2396,7 @@
         <v>264</v>
       </c>
       <c r="D36" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2410,7 +2410,7 @@
         <v>264</v>
       </c>
       <c r="D37" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2424,7 +2424,7 @@
         <v>264</v>
       </c>
       <c r="D38" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2438,7 +2438,7 @@
         <v>264</v>
       </c>
       <c r="D39" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2452,7 +2452,7 @@
         <v>266</v>
       </c>
       <c r="D40" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2466,7 +2466,7 @@
         <v>264</v>
       </c>
       <c r="D41" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2480,7 +2480,7 @@
         <v>264</v>
       </c>
       <c r="D42" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2494,7 +2494,7 @@
         <v>264</v>
       </c>
       <c r="D43" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2508,7 +2508,7 @@
         <v>265</v>
       </c>
       <c r="D44" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2522,7 +2522,7 @@
         <v>264</v>
       </c>
       <c r="D45" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2536,7 +2536,7 @@
         <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2550,7 +2550,7 @@
         <v>267</v>
       </c>
       <c r="D47" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2564,7 +2564,7 @@
         <v>268</v>
       </c>
       <c r="D48" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2578,7 +2578,7 @@
         <v>268</v>
       </c>
       <c r="D49" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2592,7 +2592,7 @@
         <v>264</v>
       </c>
       <c r="D50" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2606,7 +2606,7 @@
         <v>264</v>
       </c>
       <c r="D51" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2620,7 +2620,7 @@
         <v>264</v>
       </c>
       <c r="D52" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2634,7 +2634,7 @@
         <v>264</v>
       </c>
       <c r="D53" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2648,7 +2648,7 @@
         <v>264</v>
       </c>
       <c r="D54" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2662,7 +2662,7 @@
         <v>264</v>
       </c>
       <c r="D55" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2676,7 +2676,7 @@
         <v>264</v>
       </c>
       <c r="D56" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2690,7 +2690,7 @@
         <v>264</v>
       </c>
       <c r="D57" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2704,7 +2704,7 @@
         <v>264</v>
       </c>
       <c r="D58" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2718,7 +2718,7 @@
         <v>264</v>
       </c>
       <c r="D59" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2732,7 +2732,7 @@
         <v>264</v>
       </c>
       <c r="D60" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2746,7 +2746,7 @@
         <v>264</v>
       </c>
       <c r="D61" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2760,7 +2760,7 @@
         <v>264</v>
       </c>
       <c r="D62" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2774,7 +2774,7 @@
         <v>268</v>
       </c>
       <c r="D63" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2788,7 +2788,7 @@
         <v>269</v>
       </c>
       <c r="D64" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2802,7 +2802,7 @@
         <v>264</v>
       </c>
       <c r="D65" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2816,7 +2816,7 @@
         <v>266</v>
       </c>
       <c r="D66" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2830,7 +2830,7 @@
         <v>266</v>
       </c>
       <c r="D67" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2844,7 +2844,7 @@
         <v>264</v>
       </c>
       <c r="D68" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2858,7 +2858,7 @@
         <v>268</v>
       </c>
       <c r="D69" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2872,7 +2872,7 @@
         <v>264</v>
       </c>
       <c r="D70" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2886,7 +2886,7 @@
         <v>264</v>
       </c>
       <c r="D71" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2900,7 +2900,7 @@
         <v>264</v>
       </c>
       <c r="D72" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2914,7 +2914,7 @@
         <v>266</v>
       </c>
       <c r="D73" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2928,7 +2928,7 @@
         <v>266</v>
       </c>
       <c r="D74" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2942,7 +2942,7 @@
         <v>268</v>
       </c>
       <c r="D75" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2956,7 +2956,7 @@
         <v>266</v>
       </c>
       <c r="D76" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2970,7 +2970,7 @@
         <v>264</v>
       </c>
       <c r="D77" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2984,7 +2984,7 @@
         <v>264</v>
       </c>
       <c r="D78" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2998,7 +2998,7 @@
         <v>264</v>
       </c>
       <c r="D79" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3012,7 +3012,7 @@
         <v>264</v>
       </c>
       <c r="D80" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3026,7 +3026,7 @@
         <v>264</v>
       </c>
       <c r="D81" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3040,7 +3040,7 @@
         <v>264</v>
       </c>
       <c r="D82" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3054,7 +3054,7 @@
         <v>265</v>
       </c>
       <c r="D83" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3068,7 +3068,7 @@
         <v>266</v>
       </c>
       <c r="D84" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3082,7 +3082,7 @@
         <v>264</v>
       </c>
       <c r="D85" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3096,7 +3096,7 @@
         <v>269</v>
       </c>
       <c r="D86" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3110,7 +3110,7 @@
         <v>270</v>
       </c>
       <c r="D87" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3124,7 +3124,7 @@
         <v>264</v>
       </c>
       <c r="D88" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3138,7 +3138,7 @@
         <v>264</v>
       </c>
       <c r="D89" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3152,7 +3152,7 @@
         <v>264</v>
       </c>
       <c r="D90" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3166,7 +3166,7 @@
         <v>264</v>
       </c>
       <c r="D91" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3180,7 +3180,7 @@
         <v>264</v>
       </c>
       <c r="D92" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3194,7 +3194,7 @@
         <v>264</v>
       </c>
       <c r="D93" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3205,10 +3205,10 @@
         <v>259</v>
       </c>
       <c r="C94" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="D94" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3222,7 +3222,7 @@
         <v>264</v>
       </c>
       <c r="D95" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3233,10 +3233,10 @@
         <v>259</v>
       </c>
       <c r="C96" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="D96" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3250,7 +3250,7 @@
         <v>264</v>
       </c>
       <c r="D97" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3264,7 +3264,7 @@
         <v>264</v>
       </c>
       <c r="D98" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3278,7 +3278,7 @@
         <v>264</v>
       </c>
       <c r="D99" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3292,7 +3292,7 @@
         <v>264</v>
       </c>
       <c r="D100" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3306,7 +3306,7 @@
         <v>264</v>
       </c>
       <c r="D101" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3317,10 +3317,10 @@
         <v>259</v>
       </c>
       <c r="C102" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="D102" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3334,7 +3334,7 @@
         <v>264</v>
       </c>
       <c r="D103" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3348,7 +3348,7 @@
         <v>264</v>
       </c>
       <c r="D104" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3362,7 +3362,7 @@
         <v>264</v>
       </c>
       <c r="D105" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3376,7 +3376,7 @@
         <v>264</v>
       </c>
       <c r="D106" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3390,7 +3390,7 @@
         <v>264</v>
       </c>
       <c r="D107" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3404,7 +3404,7 @@
         <v>264</v>
       </c>
       <c r="D108" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3418,7 +3418,7 @@
         <v>264</v>
       </c>
       <c r="D109" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3432,7 +3432,7 @@
         <v>264</v>
       </c>
       <c r="D110" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3446,7 +3446,7 @@
         <v>264</v>
       </c>
       <c r="D111" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3460,7 +3460,7 @@
         <v>264</v>
       </c>
       <c r="D112" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3474,7 +3474,7 @@
         <v>264</v>
       </c>
       <c r="D113" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3488,7 +3488,7 @@
         <v>264</v>
       </c>
       <c r="D114" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3502,7 +3502,7 @@
         <v>264</v>
       </c>
       <c r="D115" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3516,7 +3516,7 @@
         <v>264</v>
       </c>
       <c r="D116" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3530,7 +3530,7 @@
         <v>264</v>
       </c>
       <c r="D117" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3544,7 +3544,7 @@
         <v>264</v>
       </c>
       <c r="D118" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3558,7 +3558,7 @@
         <v>264</v>
       </c>
       <c r="D119" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3572,7 +3572,7 @@
         <v>264</v>
       </c>
       <c r="D120" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3586,7 +3586,7 @@
         <v>267</v>
       </c>
       <c r="D121" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3600,7 +3600,7 @@
         <v>267</v>
       </c>
       <c r="D122" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3614,7 +3614,7 @@
         <v>264</v>
       </c>
       <c r="D123" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3628,7 +3628,7 @@
         <v>268</v>
       </c>
       <c r="D124" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3642,7 +3642,7 @@
         <v>264</v>
       </c>
       <c r="D125" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3656,7 +3656,7 @@
         <v>264</v>
       </c>
       <c r="D126" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3670,7 +3670,7 @@
         <v>264</v>
       </c>
       <c r="D127" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3684,7 +3684,7 @@
         <v>264</v>
       </c>
       <c r="D128" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3698,7 +3698,7 @@
         <v>264</v>
       </c>
       <c r="D129" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3712,7 +3712,7 @@
         <v>264</v>
       </c>
       <c r="D130" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3726,7 +3726,7 @@
         <v>264</v>
       </c>
       <c r="D131" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3737,10 +3737,10 @@
         <v>259</v>
       </c>
       <c r="C132" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="D132" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3754,7 +3754,7 @@
         <v>264</v>
       </c>
       <c r="D133" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3768,7 +3768,7 @@
         <v>264</v>
       </c>
       <c r="D134" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3782,7 +3782,7 @@
         <v>264</v>
       </c>
       <c r="D135" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3796,7 +3796,7 @@
         <v>264</v>
       </c>
       <c r="D136" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3810,7 +3810,7 @@
         <v>266</v>
       </c>
       <c r="D137" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3824,7 +3824,7 @@
         <v>266</v>
       </c>
       <c r="D138" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3838,7 +3838,7 @@
         <v>264</v>
       </c>
       <c r="D139" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3852,7 +3852,7 @@
         <v>264</v>
       </c>
       <c r="D140" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3866,7 +3866,7 @@
         <v>264</v>
       </c>
       <c r="D141" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3880,7 +3880,7 @@
         <v>264</v>
       </c>
       <c r="D142" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3894,7 +3894,7 @@
         <v>264</v>
       </c>
       <c r="D143" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3908,7 +3908,7 @@
         <v>264</v>
       </c>
       <c r="D144" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3922,7 +3922,7 @@
         <v>264</v>
       </c>
       <c r="D145" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3936,7 +3936,7 @@
         <v>264</v>
       </c>
       <c r="D146" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3950,7 +3950,7 @@
         <v>264</v>
       </c>
       <c r="D147" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3964,7 +3964,7 @@
         <v>265</v>
       </c>
       <c r="D148" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3978,7 +3978,7 @@
         <v>264</v>
       </c>
       <c r="D149" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3992,7 +3992,7 @@
         <v>264</v>
       </c>
       <c r="D150" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4006,7 +4006,7 @@
         <v>264</v>
       </c>
       <c r="D151" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4020,7 +4020,7 @@
         <v>264</v>
       </c>
       <c r="D152" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4034,7 +4034,7 @@
         <v>264</v>
       </c>
       <c r="D153" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4045,10 +4045,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="D154" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4062,7 +4062,7 @@
         <v>265</v>
       </c>
       <c r="D155" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4073,10 +4073,10 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="D156" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4090,7 +4090,7 @@
         <v>264</v>
       </c>
       <c r="D157" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4104,7 +4104,7 @@
         <v>264</v>
       </c>
       <c r="D158" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4118,7 +4118,7 @@
         <v>264</v>
       </c>
       <c r="D159" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4132,7 +4132,7 @@
         <v>264</v>
       </c>
       <c r="D160" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4146,7 +4146,7 @@
         <v>264</v>
       </c>
       <c r="D161" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4160,7 +4160,7 @@
         <v>264</v>
       </c>
       <c r="D162" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4174,7 +4174,7 @@
         <v>264</v>
       </c>
       <c r="D163" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4188,7 +4188,7 @@
         <v>264</v>
       </c>
       <c r="D164" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4202,7 +4202,7 @@
         <v>264</v>
       </c>
       <c r="D165" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4216,7 +4216,7 @@
         <v>264</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4230,7 +4230,7 @@
         <v>264</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4244,7 +4244,7 @@
         <v>264</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4258,7 +4258,7 @@
         <v>264</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4272,7 +4272,7 @@
         <v>264</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4286,7 +4286,7 @@
         <v>264</v>
       </c>
       <c r="D171" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4300,7 +4300,7 @@
         <v>264</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4314,7 +4314,7 @@
         <v>264</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4328,7 +4328,7 @@
         <v>264</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4342,7 +4342,7 @@
         <v>264</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4356,7 +4356,7 @@
         <v>264</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4370,7 +4370,7 @@
         <v>264</v>
       </c>
       <c r="D177" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4384,7 +4384,7 @@
         <v>264</v>
       </c>
       <c r="D178" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4398,7 +4398,7 @@
         <v>264</v>
       </c>
       <c r="D179" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4412,7 +4412,7 @@
         <v>264</v>
       </c>
       <c r="D180" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4426,7 +4426,7 @@
         <v>264</v>
       </c>
       <c r="D181" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4440,7 +4440,7 @@
         <v>264</v>
       </c>
       <c r="D182" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4454,7 +4454,7 @@
         <v>264</v>
       </c>
       <c r="D183" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4468,7 +4468,7 @@
         <v>264</v>
       </c>
       <c r="D184" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4482,7 +4482,7 @@
         <v>264</v>
       </c>
       <c r="D185" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4496,7 +4496,7 @@
         <v>264</v>
       </c>
       <c r="D186" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4510,7 +4510,7 @@
         <v>264</v>
       </c>
       <c r="D187" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4524,7 +4524,7 @@
         <v>264</v>
       </c>
       <c r="D188" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4538,7 +4538,7 @@
         <v>264</v>
       </c>
       <c r="D189" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4552,7 +4552,7 @@
         <v>264</v>
       </c>
       <c r="D190" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4566,7 +4566,7 @@
         <v>264</v>
       </c>
       <c r="D191" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4580,7 +4580,7 @@
         <v>264</v>
       </c>
       <c r="D192" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4594,7 +4594,7 @@
         <v>264</v>
       </c>
       <c r="D193" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4608,7 +4608,7 @@
         <v>264</v>
       </c>
       <c r="D194" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4622,7 +4622,7 @@
         <v>264</v>
       </c>
       <c r="D195" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4636,7 +4636,7 @@
         <v>264</v>
       </c>
       <c r="D196" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4650,7 +4650,7 @@
         <v>264</v>
       </c>
       <c r="D197" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4664,7 +4664,7 @@
         <v>264</v>
       </c>
       <c r="D198" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4678,7 +4678,7 @@
         <v>264</v>
       </c>
       <c r="D199" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4692,7 +4692,7 @@
         <v>264</v>
       </c>
       <c r="D200" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4706,7 +4706,7 @@
         <v>264</v>
       </c>
       <c r="D201" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4720,7 +4720,7 @@
         <v>264</v>
       </c>
       <c r="D202" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4734,7 +4734,7 @@
         <v>264</v>
       </c>
       <c r="D203" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4748,7 +4748,7 @@
         <v>264</v>
       </c>
       <c r="D204" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4762,7 +4762,7 @@
         <v>264</v>
       </c>
       <c r="D205" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4776,7 +4776,7 @@
         <v>264</v>
       </c>
       <c r="D206" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4790,7 +4790,7 @@
         <v>264</v>
       </c>
       <c r="D207" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4804,7 +4804,7 @@
         <v>264</v>
       </c>
       <c r="D208" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4818,7 +4818,7 @@
         <v>264</v>
       </c>
       <c r="D209" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4832,7 +4832,7 @@
         <v>264</v>
       </c>
       <c r="D210" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4846,7 +4846,7 @@
         <v>266</v>
       </c>
       <c r="D211" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4860,7 +4860,7 @@
         <v>264</v>
       </c>
       <c r="D212" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4874,7 +4874,7 @@
         <v>264</v>
       </c>
       <c r="D213" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4888,7 +4888,7 @@
         <v>264</v>
       </c>
       <c r="D214" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4902,7 +4902,7 @@
         <v>264</v>
       </c>
       <c r="D215" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4916,7 +4916,7 @@
         <v>264</v>
       </c>
       <c r="D216" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4930,7 +4930,7 @@
         <v>264</v>
       </c>
       <c r="D217" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4944,7 +4944,7 @@
         <v>264</v>
       </c>
       <c r="D218" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4958,7 +4958,7 @@
         <v>264</v>
       </c>
       <c r="D219" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4972,7 +4972,7 @@
         <v>264</v>
       </c>
       <c r="D220" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4986,7 +4986,7 @@
         <v>264</v>
       </c>
       <c r="D221" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5000,7 +5000,7 @@
         <v>264</v>
       </c>
       <c r="D222" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5014,7 +5014,7 @@
         <v>264</v>
       </c>
       <c r="D223" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5028,7 +5028,7 @@
         <v>266</v>
       </c>
       <c r="D224" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5042,7 +5042,7 @@
         <v>264</v>
       </c>
       <c r="D225" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5056,7 +5056,7 @@
         <v>264</v>
       </c>
       <c r="D226" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5070,7 +5070,7 @@
         <v>266</v>
       </c>
       <c r="D227" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5084,7 +5084,7 @@
         <v>264</v>
       </c>
       <c r="D228" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5098,7 +5098,7 @@
         <v>266</v>
       </c>
       <c r="D229" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5112,7 +5112,7 @@
         <v>264</v>
       </c>
       <c r="D230" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5126,7 +5126,7 @@
         <v>264</v>
       </c>
       <c r="D231" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5140,7 +5140,7 @@
         <v>264</v>
       </c>
       <c r="D232" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5154,7 +5154,7 @@
         <v>264</v>
       </c>
       <c r="D233" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5168,7 +5168,7 @@
         <v>264</v>
       </c>
       <c r="D234" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5182,7 +5182,7 @@
         <v>264</v>
       </c>
       <c r="D235" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5196,7 +5196,7 @@
         <v>264</v>
       </c>
       <c r="D236" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5210,7 +5210,7 @@
         <v>264</v>
       </c>
       <c r="D237" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5224,7 +5224,7 @@
         <v>264</v>
       </c>
       <c r="D238" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5238,7 +5238,7 @@
         <v>264</v>
       </c>
       <c r="D239" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5252,7 +5252,7 @@
         <v>264</v>
       </c>
       <c r="D240" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5266,7 +5266,7 @@
         <v>264</v>
       </c>
       <c r="D241" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5280,7 +5280,7 @@
         <v>264</v>
       </c>
       <c r="D242" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5294,7 +5294,7 @@
         <v>264</v>
       </c>
       <c r="D243" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5308,7 +5308,7 @@
         <v>264</v>
       </c>
       <c r="D244" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5322,7 +5322,7 @@
         <v>264</v>
       </c>
       <c r="D245" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5336,7 +5336,7 @@
         <v>264</v>
       </c>
       <c r="D246" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5350,7 +5350,7 @@
         <v>264</v>
       </c>
       <c r="D247" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5364,7 +5364,7 @@
         <v>264</v>
       </c>
       <c r="D248" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5378,7 +5378,7 @@
         <v>264</v>
       </c>
       <c r="D249" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5392,7 +5392,7 @@
         <v>266</v>
       </c>
       <c r="D250" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5406,7 +5406,7 @@
         <v>264</v>
       </c>
       <c r="D251" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5420,7 +5420,7 @@
         <v>264</v>
       </c>
       <c r="D252" t="s">
-        <v>502</v>
+        <v>434</v>
       </c>
     </row>
     <row r="253" spans="1:4">
